--- a/tests/datatest/ListPriceFloat.xlsx
+++ b/tests/datatest/ListPriceFloat.xlsx
@@ -4,12 +4,15 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12330" activeTab="2"/>
+    <workbookView windowWidth="29010" windowHeight="13260" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="List token" sheetId="4" r:id="rId1"/>
     <sheet name="Market info all" sheetId="2" r:id="rId2"/>
     <sheet name="Market info" sheetId="3" r:id="rId3"/>
+    <sheet name="Market info BK3" sheetId="7" r:id="rId4"/>
+    <sheet name="Market info BK2" sheetId="6" r:id="rId5"/>
+    <sheet name="Pool &amp; dToken" sheetId="5" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Market info all'!$A$1:$H$1013</definedName>
@@ -19,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9619" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10235" uniqueCount="211">
   <si>
     <t>token</t>
   </si>
@@ -579,10 +582,79 @@
     <t>814de8a99452972a9fa9fe2c0f59f49697f208005c001ecac1ddfd57.7fdbe575c2d6fa85fd8c20d714be2470f2b2b83f976c6fa2118e1074</t>
   </si>
   <si>
+    <t>1f3aec8bfe7ea4fe14c5f121e2a92e301afe414147860d557cac7e34.5553444378</t>
+  </si>
+  <si>
+    <t>USDCx</t>
+  </si>
+  <si>
+    <t>94dca24a1f1fcc2ff51cd90f32f4fe9e786d861a2dbf7d27598d26e8.11bbbea6a20e0cb0433fc7723e16427d435c298e1b7304365af6b3e6</t>
+  </si>
+  <si>
+    <t>dUSDCx</t>
+  </si>
+  <si>
     <t>9759bfd89ffa91652064f3a2ef66dcc5c52ca85b55e938ad29198f72</t>
   </si>
   <si>
     <t>sADA</t>
+  </si>
+  <si>
+    <t>dSURF</t>
+  </si>
+  <si>
+    <t>94dca24a1f1fcc2ff51cd90f32f4fe9e786d861a2dbf7d27598d26e8.5f6c47af012a8df6b79a7927d598ed4f59745f9c653a5440656800e3</t>
+  </si>
+  <si>
+    <t>dETH</t>
+  </si>
+  <si>
+    <t>dUSDT</t>
+  </si>
+  <si>
+    <t>dUSDC</t>
+  </si>
+  <si>
+    <t>dBTC</t>
+  </si>
+  <si>
+    <t>94dca24a1f1fcc2ff51cd90f32f4fe9e786d861a2dbf7d27598d26e8.fc7f95ea342aff20a4fed512e4b7805003641c483af3e4a379e8eccb</t>
+  </si>
+  <si>
+    <t>dNIGHT</t>
+  </si>
+  <si>
+    <t>73f29518da0013a671458d52624a4828c5b5bedaff8a950b0063b1cf.57acdd5c0dfbdec9d2d611f57f42951b78ef8fe7dc1935b9ce19d839</t>
+  </si>
+  <si>
+    <t>dUSDM.v2</t>
+  </si>
+  <si>
+    <t>73f29518da0013a671458d52624a4828c5b5bedaff8a950b0063b1cf.506b019656c07487e4c2a752378b8c8cfdb4f673e5cfdaa10ddb8740</t>
+  </si>
+  <si>
+    <t>dBTC.v2</t>
+  </si>
+  <si>
+    <t>73f29518da0013a671458d52624a4828c5b5bedaff8a950b0063b1cf.449eab94177468bdd22eed594871a756d91be42eab3ef06625753062</t>
+  </si>
+  <si>
+    <t>dUSDA.v2</t>
+  </si>
+  <si>
+    <t>73f29518da0013a671458d52624a4828c5b5bedaff8a950b0063b1cf.fe24971839096460b051a6da5ee3a6db1224d512e1b71d4d348c1444</t>
+  </si>
+  <si>
+    <t>dNIGTH.v2</t>
+  </si>
+  <si>
+    <t>73f29518da0013a671458d52624a4828c5b5bedaff8a950b0063b1cf.f3f0f123b418b38ceebe0fab25e30d96a628d1e9b501121933c9b5de</t>
+  </si>
+  <si>
+    <t>dADA.v2</t>
+  </si>
+  <si>
+    <t>814de8a99452972a9fa9fe2c0f59f49697f208005c001ecac1ddfd57.11bbbea6a20e0cb0433fc7723e16427d435c298e1b7304365af6b3e6</t>
   </si>
 </sst>
 </file>
@@ -592,8 +664,8 @@
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_-* #,##0\ &quot;₫&quot;_-;\-* #,##0\ &quot;₫&quot;_-;_-* &quot;-&quot;\ &quot;₫&quot;_-;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_-* #,##0.00\ &quot;₫&quot;_-;\-* #,##0.00\ &quot;₫&quot;_-;_-* &quot;-&quot;??\ &quot;₫&quot;_-;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -611,16 +683,30 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF0000FF"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -636,14 +722,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -657,15 +736,25 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -679,11 +768,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -696,30 +784,22 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="Calibri"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -741,15 +821,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C6500"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -764,7 +836,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -776,7 +866,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -788,19 +914,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -812,13 +986,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -830,61 +998,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -896,65 +1010,38 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -973,10 +1060,36 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -1008,32 +1121,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1073,13 +1160,13 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1091,136 +1178,139 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="10" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1612,578 +1702,578 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="2" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="2" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:2">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="2" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:2">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="2" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:2">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="2" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:2">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="2" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:2">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="2" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:2">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="2" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="2" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:2">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" s="2" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="2" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="15" spans="1:2">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" s="2" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:2">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" s="2" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="17" spans="1:2">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" s="2" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="18" spans="1:2">
-      <c r="A18" s="1" t="s">
+      <c r="A18" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B18" s="2" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="19" spans="1:2">
-      <c r="A19" s="1" t="s">
+      <c r="A19" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B19" s="2" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="20" spans="1:2">
-      <c r="A20" s="1" t="s">
+      <c r="A20" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B20" s="2" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="21" spans="1:2">
-      <c r="A21" s="1" t="s">
+      <c r="A21" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B21" s="2" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="22" spans="1:2">
-      <c r="A22" s="1" t="s">
+      <c r="A22" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B22" s="2" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="23" spans="1:2">
-      <c r="A23" s="1" t="s">
+      <c r="A23" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B23" s="2" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="24" spans="1:2">
-      <c r="A24" s="1" t="s">
+      <c r="A24" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="B24" s="2" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:2">
-      <c r="A25" s="1" t="s">
+      <c r="A25" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="B25" s="2" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="26" spans="1:2">
-      <c r="A26" s="1" t="s">
+      <c r="A26" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="B26" s="2" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="27" spans="1:2">
-      <c r="A27" s="1" t="s">
+      <c r="A27" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="B27" s="2" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="28" spans="1:2">
-      <c r="A28" s="1" t="s">
+      <c r="A28" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="B28" s="2" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="29" spans="1:2">
-      <c r="A29" s="1" t="s">
+      <c r="A29" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="B29" s="2" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="30" spans="1:2">
-      <c r="A30" s="1" t="s">
+      <c r="A30" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="B30" s="2" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="31" spans="1:2">
-      <c r="A31" s="1" t="s">
+      <c r="A31" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="B31" s="2" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="32" spans="1:2">
-      <c r="A32" s="1" t="s">
+      <c r="A32" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="B32" s="2" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="33" spans="1:2">
-      <c r="A33" s="1" t="s">
+      <c r="A33" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="B33" s="2" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="34" spans="1:2">
-      <c r="A34" s="1" t="s">
+      <c r="A34" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="B34" s="2" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="35" spans="1:2">
-      <c r="A35" s="1" t="s">
+      <c r="A35" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="B35" s="2" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="36" spans="1:2">
-      <c r="A36" s="1" t="s">
+      <c r="A36" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="B36" s="2" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="37" spans="1:2">
-      <c r="A37" s="1" t="s">
+      <c r="A37" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="B37" s="2" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="38" spans="1:2">
-      <c r="A38" s="1" t="s">
+      <c r="A38" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="B38" s="1" t="s">
+      <c r="B38" s="2" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="39" spans="1:2">
-      <c r="A39" s="1" t="s">
+      <c r="A39" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="B39" s="1" t="s">
+      <c r="B39" s="2" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="40" spans="1:2">
-      <c r="A40" s="1" t="s">
+      <c r="A40" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B40" s="1" t="s">
+      <c r="B40" s="2" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="41" spans="1:2">
-      <c r="A41" s="1" t="s">
+      <c r="A41" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="B41" s="1" t="s">
+      <c r="B41" s="2" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="42" spans="1:2">
-      <c r="A42" s="1" t="s">
+      <c r="A42" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="B42" s="1" t="s">
+      <c r="B42" s="2" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="43" spans="1:2">
-      <c r="A43" s="1" t="s">
+      <c r="A43" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="B43" s="1" t="s">
+      <c r="B43" s="2" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="44" spans="1:2">
-      <c r="A44" s="1" t="s">
+      <c r="A44" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="B44" s="1" t="s">
+      <c r="B44" s="2" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="45" spans="1:2">
-      <c r="A45" s="1" t="s">
+      <c r="A45" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="B45" s="1" t="s">
+      <c r="B45" s="2" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="46" spans="1:2">
-      <c r="A46" s="1" t="s">
+      <c r="A46" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="B46" s="1" t="s">
+      <c r="B46" s="2" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="47" spans="1:2">
-      <c r="A47" s="1" t="s">
+      <c r="A47" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="B47" s="1" t="s">
+      <c r="B47" s="2" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="48" spans="1:2">
-      <c r="A48" s="1" t="s">
+      <c r="A48" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="B48" s="1" t="s">
+      <c r="B48" s="2" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="49" spans="1:2">
-      <c r="A49" s="1" t="s">
+      <c r="A49" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="B49" s="1" t="s">
+      <c r="B49" s="2" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="50" spans="1:2">
-      <c r="A50" s="1" t="s">
+      <c r="A50" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B50" s="1" t="s">
+      <c r="B50" s="2" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="51" spans="1:2">
-      <c r="A51" s="1" t="s">
+      <c r="A51" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="B51" s="1" t="s">
+      <c r="B51" s="2" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="52" spans="1:2">
-      <c r="A52" s="1" t="s">
+      <c r="A52" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="B52" s="1" t="s">
+      <c r="B52" s="2" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="53" spans="1:2">
-      <c r="A53" s="1" t="s">
+      <c r="A53" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="B53" s="1" t="s">
+      <c r="B53" s="2" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="54" spans="1:2">
-      <c r="A54" s="1" t="s">
+      <c r="A54" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="B54" s="1" t="s">
+      <c r="B54" s="2" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="55" spans="1:2">
-      <c r="A55" s="1" t="s">
+      <c r="A55" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="B55" s="1" t="s">
+      <c r="B55" s="2" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="56" spans="1:2">
-      <c r="A56" s="1" t="s">
+      <c r="A56" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="B56" s="1" t="s">
+      <c r="B56" s="2" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="57" spans="1:2">
-      <c r="A57" s="1" t="s">
+      <c r="A57" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="B57" s="1" t="s">
+      <c r="B57" s="2" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="58" spans="1:2">
-      <c r="A58" s="1" t="s">
+      <c r="A58" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="B58" s="1" t="s">
+      <c r="B58" s="2" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="59" spans="1:2">
-      <c r="A59" s="1" t="s">
+      <c r="A59" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="B59" s="1" t="s">
+      <c r="B59" s="2" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="60" spans="1:2">
-      <c r="A60" s="1" t="s">
+      <c r="A60" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="B60" s="1" t="s">
+      <c r="B60" s="2" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="61" spans="1:2">
-      <c r="A61" s="1" t="s">
+      <c r="A61" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="B61" s="1" t="s">
+      <c r="B61" s="2" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="62" spans="1:2">
-      <c r="A62" s="1" t="s">
+      <c r="A62" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="B62" s="1" t="s">
+      <c r="B62" s="2" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="63" spans="1:2">
-      <c r="A63" s="1" t="s">
+      <c r="A63" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="B63" s="1" t="s">
+      <c r="B63" s="2" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="64" spans="1:2">
-      <c r="A64" s="1" t="s">
+      <c r="A64" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="B64" s="1" t="s">
+      <c r="B64" s="2" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="65" spans="1:2">
-      <c r="A65" s="1" t="s">
+      <c r="A65" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="B65" s="1" t="s">
+      <c r="B65" s="2" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="66" spans="1:2">
-      <c r="A66" s="1" t="s">
+      <c r="A66" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="B66" s="1" t="s">
+      <c r="B66" s="2" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="67" spans="1:2">
-      <c r="A67" s="1" t="s">
+      <c r="A67" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="B67" s="1" t="s">
+      <c r="B67" s="2" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="68" spans="1:2">
-      <c r="A68" s="1" t="s">
+      <c r="A68" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="B68" s="1" t="s">
+      <c r="B68" s="2" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="69" spans="1:2">
-      <c r="A69" s="1" t="s">
+      <c r="A69" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="B69" s="1" t="s">
+      <c r="B69" s="2" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="70" spans="1:2">
-      <c r="A70" s="1" t="s">
+      <c r="A70" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="B70" s="1" t="s">
+      <c r="B70" s="2" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="71" spans="1:2">
-      <c r="A71" s="1" t="s">
+      <c r="A71" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="B71" s="1" t="s">
+      <c r="B71" s="2" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="72" spans="1:2">
-      <c r="A72" s="1" t="s">
+      <c r="A72" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="B72" s="1" t="s">
+      <c r="B72" s="2" t="s">
         <v>143</v>
       </c>
     </row>
@@ -2193,282 +2283,282 @@
       </c>
     </row>
     <row r="76" spans="1:4">
-      <c r="A76" s="1" t="s">
+      <c r="A76" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B76" s="1" t="s">
+      <c r="B76" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C76" s="1" t="s">
+      <c r="C76" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="D76" s="1" t="s">
+      <c r="D76" s="2" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="77" spans="1:4">
-      <c r="A77" s="1" t="s">
+      <c r="A77" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B77" s="1" t="s">
+      <c r="B77" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C77" s="1" t="s">
+      <c r="C77" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="D77" s="1" t="s">
+      <c r="D77" s="2" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="78" spans="1:4">
-      <c r="A78" s="1" t="s">
+      <c r="A78" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="B78" s="1" t="s">
+      <c r="B78" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="C78" s="1" t="s">
+      <c r="C78" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D78" s="1" t="s">
+      <c r="D78" s="2" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="79" spans="1:4">
-      <c r="A79" s="1" t="s">
+      <c r="A79" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B79" s="1" t="s">
+      <c r="B79" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C79" s="1" t="s">
+      <c r="C79" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="D79" s="1" t="s">
+      <c r="D79" s="2" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="80" spans="1:4">
-      <c r="A80" s="1" t="s">
+      <c r="A80" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B80" s="1" t="s">
+      <c r="B80" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C80" s="1" t="s">
+      <c r="C80" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="D80" s="1" t="s">
+      <c r="D80" s="2" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="81" spans="1:4">
-      <c r="A81" s="1" t="s">
+      <c r="A81" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="B81" s="1" t="s">
+      <c r="B81" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C81" s="1" t="s">
+      <c r="C81" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="D81" s="1" t="s">
+      <c r="D81" s="2" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="82" spans="1:4">
-      <c r="A82" s="1" t="s">
+      <c r="A82" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B82" s="1" t="s">
+      <c r="B82" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="C82" s="1" t="s">
+      <c r="C82" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="D82" s="1" t="s">
+      <c r="D82" s="2" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="83" spans="1:4">
-      <c r="A83" s="1" t="s">
+      <c r="A83" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="B83" s="1" t="s">
+      <c r="B83" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C83" s="1" t="s">
+      <c r="C83" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="D83" s="1" t="s">
+      <c r="D83" s="2" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="84" spans="1:4">
-      <c r="A84" s="1" t="s">
+      <c r="A84" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="B84" s="1" t="s">
+      <c r="B84" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C84" s="1" t="s">
+      <c r="C84" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="D84" s="1" t="s">
+      <c r="D84" s="2" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="85" spans="1:4">
-      <c r="A85" s="1" t="s">
+      <c r="A85" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="B85" s="1" t="s">
+      <c r="B85" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C85" s="1" t="s">
+      <c r="C85" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="D85" s="1" t="s">
+      <c r="D85" s="2" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="86" spans="1:4">
-      <c r="A86" s="1" t="s">
+      <c r="A86" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="B86" s="1" t="s">
+      <c r="B86" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C86" s="1" t="s">
+      <c r="C86" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="D86" s="1" t="s">
+      <c r="D86" s="2" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="87" spans="1:4">
-      <c r="A87" s="1" t="s">
+      <c r="A87" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="B87" s="1" t="s">
+      <c r="B87" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="C87" s="1" t="s">
+      <c r="C87" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="D87" s="1" t="s">
+      <c r="D87" s="2" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="88" spans="1:4">
-      <c r="A88" s="1" t="s">
+      <c r="A88" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="B88" s="1" t="s">
+      <c r="B88" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C88" s="1" t="s">
+      <c r="C88" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="D88" s="1" t="s">
+      <c r="D88" s="2" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="89" spans="1:4">
-      <c r="A89" s="1" t="s">
+      <c r="A89" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B89" s="1" t="s">
+      <c r="B89" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C89" s="1" t="s">
+      <c r="C89" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="D89" s="1" t="s">
+      <c r="D89" s="2" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="90" spans="1:4">
-      <c r="A90" s="1" t="s">
+      <c r="A90" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="B90" s="1" t="s">
+      <c r="B90" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C90" s="1" t="s">
+      <c r="C90" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="D90" s="1" t="s">
+      <c r="D90" s="2" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="91" spans="1:4">
-      <c r="A91" s="1" t="s">
+      <c r="A91" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="B91" s="1" t="s">
+      <c r="B91" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C91" s="1" t="s">
+      <c r="C91" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="D91" s="1" t="s">
+      <c r="D91" s="2" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="92" spans="1:4">
-      <c r="A92" s="1" t="s">
+      <c r="A92" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="B92" s="1" t="s">
+      <c r="B92" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="C92" s="1" t="s">
+      <c r="C92" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="D92" s="1" t="s">
+      <c r="D92" s="2" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="93" spans="1:4">
-      <c r="A93" s="1" t="s">
+      <c r="A93" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="B93" s="1" t="s">
+      <c r="B93" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="C93" s="1" t="s">
+      <c r="C93" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="D93" s="1" t="s">
+      <c r="D93" s="2" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="94" spans="1:4">
-      <c r="A94" s="1" t="s">
+      <c r="A94" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="B94" s="1" t="s">
+      <c r="B94" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C94" s="1" t="s">
+      <c r="C94" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="D94" s="1" t="s">
+      <c r="D94" s="2" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="95" spans="1:4">
-      <c r="A95" s="1" t="s">
+      <c r="A95" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="B95" s="1" t="s">
+      <c r="B95" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="C95" s="1" t="s">
+      <c r="C95" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="D95" s="1" t="s">
+      <c r="D95" s="2" t="s">
         <v>143</v>
       </c>
     </row>
@@ -2480,7 +2570,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr filterMode="1"/>
+  <sheetPr/>
   <dimension ref="A1:H1013"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75" outlineLevelCol="7"/>
   <cols>
@@ -19148,7 +19238,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="725" hidden="1" spans="1:7">
+    <row r="725" spans="1:7">
       <c r="A725" t="s">
         <v>173</v>
       </c>
@@ -19217,7 +19307,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="728" hidden="1" spans="1:7">
+    <row r="728" spans="1:7">
       <c r="A728" t="s">
         <v>173</v>
       </c>
@@ -19240,7 +19330,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="729" hidden="1" spans="1:7">
+    <row r="729" spans="1:7">
       <c r="A729" t="s">
         <v>173</v>
       </c>
@@ -19286,7 +19376,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="731" hidden="1" spans="1:7">
+    <row r="731" spans="1:7">
       <c r="A731" t="s">
         <v>173</v>
       </c>
@@ -19401,7 +19491,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="736" hidden="1" spans="1:7">
+    <row r="736" spans="1:7">
       <c r="A736" t="s">
         <v>173</v>
       </c>
@@ -19447,7 +19537,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="738" hidden="1" spans="1:7">
+    <row r="738" spans="1:7">
       <c r="A738" t="s">
         <v>173</v>
       </c>
@@ -19470,7 +19560,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="739" hidden="1" spans="1:7">
+    <row r="739" spans="1:7">
       <c r="A739" t="s">
         <v>173</v>
       </c>
@@ -19493,7 +19583,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="740" hidden="1" spans="1:7">
+    <row r="740" spans="1:7">
       <c r="A740" t="s">
         <v>173</v>
       </c>
@@ -19516,7 +19606,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="741" hidden="1" spans="1:7">
+    <row r="741" spans="1:7">
       <c r="A741" t="s">
         <v>173</v>
       </c>
@@ -19539,7 +19629,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="742" hidden="1" spans="1:7">
+    <row r="742" spans="1:7">
       <c r="A742" t="s">
         <v>173</v>
       </c>
@@ -19585,7 +19675,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="744" hidden="1" spans="1:7">
+    <row r="744" spans="1:7">
       <c r="A744" t="s">
         <v>173</v>
       </c>
@@ -19654,7 +19744,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="747" hidden="1" spans="1:7">
+    <row r="747" spans="1:7">
       <c r="A747" t="s">
         <v>173</v>
       </c>
@@ -19677,7 +19767,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="748" hidden="1" spans="1:7">
+    <row r="748" spans="1:7">
       <c r="A748" t="s">
         <v>173</v>
       </c>
@@ -19700,7 +19790,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="749" hidden="1" spans="1:7">
+    <row r="749" spans="1:7">
       <c r="A749" t="s">
         <v>173</v>
       </c>
@@ -19723,7 +19813,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="750" hidden="1" spans="1:7">
+    <row r="750" spans="1:7">
       <c r="A750" t="s">
         <v>173</v>
       </c>
@@ -19746,7 +19836,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="751" hidden="1" spans="1:7">
+    <row r="751" spans="1:7">
       <c r="A751" t="s">
         <v>173</v>
       </c>
@@ -19907,7 +19997,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="758" hidden="1" spans="1:7">
+    <row r="758" spans="1:7">
       <c r="A758" t="s">
         <v>173</v>
       </c>
@@ -19930,7 +20020,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="759" hidden="1" spans="1:7">
+    <row r="759" spans="1:7">
       <c r="A759" t="s">
         <v>173</v>
       </c>
@@ -19953,7 +20043,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="760" hidden="1" spans="1:7">
+    <row r="760" spans="1:7">
       <c r="A760" t="s">
         <v>173</v>
       </c>
@@ -19976,7 +20066,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="761" hidden="1" spans="1:7">
+    <row r="761" spans="1:7">
       <c r="A761" t="s">
         <v>173</v>
       </c>
@@ -19999,7 +20089,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="762" hidden="1" spans="1:7">
+    <row r="762" spans="1:7">
       <c r="A762" t="s">
         <v>173</v>
       </c>
@@ -20022,7 +20112,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="763" hidden="1" spans="1:7">
+    <row r="763" spans="1:7">
       <c r="A763" t="s">
         <v>173</v>
       </c>
@@ -20068,7 +20158,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="765" hidden="1" spans="1:7">
+    <row r="765" spans="1:7">
       <c r="A765" t="s">
         <v>176</v>
       </c>
@@ -20091,7 +20181,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="766" hidden="1" spans="1:7">
+    <row r="766" spans="1:7">
       <c r="A766" t="s">
         <v>176</v>
       </c>
@@ -20114,7 +20204,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="767" hidden="1" spans="1:7">
+    <row r="767" spans="1:7">
       <c r="A767" t="s">
         <v>176</v>
       </c>
@@ -20137,7 +20227,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="768" hidden="1" spans="1:7">
+    <row r="768" spans="1:7">
       <c r="A768" t="s">
         <v>176</v>
       </c>
@@ -20160,7 +20250,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="769" hidden="1" spans="1:7">
+    <row r="769" spans="1:7">
       <c r="A769" t="s">
         <v>176</v>
       </c>
@@ -20183,7 +20273,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="770" hidden="1" spans="1:7">
+    <row r="770" spans="1:7">
       <c r="A770" t="s">
         <v>176</v>
       </c>
@@ -20206,7 +20296,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="771" hidden="1" spans="1:7">
+    <row r="771" spans="1:7">
       <c r="A771" t="s">
         <v>176</v>
       </c>
@@ -20252,7 +20342,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="773" hidden="1" spans="1:7">
+    <row r="773" spans="1:7">
       <c r="A773" t="s">
         <v>176</v>
       </c>
@@ -20344,7 +20434,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="777" hidden="1" spans="1:7">
+    <row r="777" spans="1:7">
       <c r="A777" t="s">
         <v>176</v>
       </c>
@@ -20390,7 +20480,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="779" hidden="1" spans="1:7">
+    <row r="779" spans="1:7">
       <c r="A779" t="s">
         <v>176</v>
       </c>
@@ -20413,7 +20503,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="780" hidden="1" spans="1:7">
+    <row r="780" spans="1:7">
       <c r="A780" t="s">
         <v>176</v>
       </c>
@@ -20459,7 +20549,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="782" hidden="1" spans="1:7">
+    <row r="782" spans="1:7">
       <c r="A782" t="s">
         <v>176</v>
       </c>
@@ -20482,7 +20572,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="783" hidden="1" spans="1:7">
+    <row r="783" spans="1:7">
       <c r="A783" t="s">
         <v>176</v>
       </c>
@@ -20505,7 +20595,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="784" hidden="1" spans="1:7">
+    <row r="784" spans="1:7">
       <c r="A784" t="s">
         <v>176</v>
       </c>
@@ -20551,7 +20641,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="786" hidden="1" spans="1:7">
+    <row r="786" spans="1:7">
       <c r="A786" t="s">
         <v>176</v>
       </c>
@@ -20597,7 +20687,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="788" hidden="1" spans="1:7">
+    <row r="788" spans="1:7">
       <c r="A788" t="s">
         <v>176</v>
       </c>
@@ -20620,7 +20710,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="789" hidden="1" spans="1:7">
+    <row r="789" spans="1:7">
       <c r="A789" t="s">
         <v>176</v>
       </c>
@@ -20643,7 +20733,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="790" hidden="1" spans="1:7">
+    <row r="790" spans="1:7">
       <c r="A790" t="s">
         <v>176</v>
       </c>
@@ -20666,7 +20756,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="791" hidden="1" spans="1:7">
+    <row r="791" spans="1:7">
       <c r="A791" t="s">
         <v>176</v>
       </c>
@@ -20689,7 +20779,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="792" hidden="1" spans="1:7">
+    <row r="792" spans="1:7">
       <c r="A792" t="s">
         <v>176</v>
       </c>
@@ -20850,7 +20940,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="799" hidden="1" spans="1:7">
+    <row r="799" spans="1:7">
       <c r="A799" t="s">
         <v>176</v>
       </c>
@@ -20873,7 +20963,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="800" hidden="1" spans="1:7">
+    <row r="800" spans="1:7">
       <c r="A800" t="s">
         <v>176</v>
       </c>
@@ -20896,7 +20986,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="801" hidden="1" spans="1:7">
+    <row r="801" spans="1:7">
       <c r="A801" t="s">
         <v>176</v>
       </c>
@@ -20919,7 +21009,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="802" hidden="1" spans="1:7">
+    <row r="802" spans="1:7">
       <c r="A802" t="s">
         <v>176</v>
       </c>
@@ -20942,7 +21032,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="803" hidden="1" spans="1:7">
+    <row r="803" spans="1:7">
       <c r="A803" t="s">
         <v>176</v>
       </c>
@@ -20965,7 +21055,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="804" hidden="1" spans="1:7">
+    <row r="804" spans="1:7">
       <c r="A804" t="s">
         <v>176</v>
       </c>
@@ -21011,7 +21101,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="806" hidden="1" spans="1:7">
+    <row r="806" spans="1:7">
       <c r="A806" t="s">
         <v>177</v>
       </c>
@@ -21034,7 +21124,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="807" hidden="1" spans="1:7">
+    <row r="807" spans="1:7">
       <c r="A807" t="s">
         <v>177</v>
       </c>
@@ -21057,7 +21147,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="808" hidden="1" spans="1:7">
+    <row r="808" spans="1:7">
       <c r="A808" t="s">
         <v>177</v>
       </c>
@@ -21080,7 +21170,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="809" hidden="1" spans="1:7">
+    <row r="809" spans="1:7">
       <c r="A809" t="s">
         <v>177</v>
       </c>
@@ -21103,7 +21193,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="810" hidden="1" spans="1:7">
+    <row r="810" spans="1:7">
       <c r="A810" t="s">
         <v>177</v>
       </c>
@@ -21126,7 +21216,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="811" hidden="1" spans="1:7">
+    <row r="811" spans="1:7">
       <c r="A811" t="s">
         <v>177</v>
       </c>
@@ -21264,7 +21354,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="817" hidden="1" spans="1:7">
+    <row r="817" spans="1:7">
       <c r="A817" t="s">
         <v>177</v>
       </c>
@@ -21287,7 +21377,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="818" hidden="1" spans="1:7">
+    <row r="818" spans="1:7">
       <c r="A818" t="s">
         <v>177</v>
       </c>
@@ -21310,7 +21400,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="819" hidden="1" spans="1:7">
+    <row r="819" spans="1:7">
       <c r="A819" t="s">
         <v>177</v>
       </c>
@@ -21333,7 +21423,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="820" hidden="1" spans="1:7">
+    <row r="820" spans="1:7">
       <c r="A820" t="s">
         <v>177</v>
       </c>
@@ -21356,7 +21446,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="821" hidden="1" spans="1:7">
+    <row r="821" spans="1:7">
       <c r="A821" t="s">
         <v>177</v>
       </c>
@@ -21448,7 +21538,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="825" hidden="1" spans="1:7">
+    <row r="825" spans="1:7">
       <c r="A825" t="s">
         <v>177</v>
       </c>
@@ -21471,7 +21561,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="826" hidden="1" spans="1:7">
+    <row r="826" spans="1:7">
       <c r="A826" t="s">
         <v>177</v>
       </c>
@@ -21494,7 +21584,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="827" hidden="1" spans="1:7">
+    <row r="827" spans="1:7">
       <c r="A827" t="s">
         <v>177</v>
       </c>
@@ -21655,7 +21745,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="834" hidden="1" spans="1:7">
+    <row r="834" spans="1:7">
       <c r="A834" t="s">
         <v>177</v>
       </c>
@@ -21678,7 +21768,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="835" hidden="1" spans="1:7">
+    <row r="835" spans="1:7">
       <c r="A835" t="s">
         <v>177</v>
       </c>
@@ -21701,7 +21791,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="836" hidden="1" spans="1:7">
+    <row r="836" spans="1:7">
       <c r="A836" t="s">
         <v>177</v>
       </c>
@@ -21724,7 +21814,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="837" hidden="1" spans="1:7">
+    <row r="837" spans="1:7">
       <c r="A837" t="s">
         <v>177</v>
       </c>
@@ -21747,7 +21837,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="838" hidden="1" spans="1:7">
+    <row r="838" spans="1:7">
       <c r="A838" t="s">
         <v>177</v>
       </c>
@@ -21770,7 +21860,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="839" hidden="1" spans="1:7">
+    <row r="839" spans="1:7">
       <c r="A839" t="s">
         <v>177</v>
       </c>
@@ -21816,7 +21906,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="841" hidden="1" spans="1:7">
+    <row r="841" spans="1:7">
       <c r="A841" t="s">
         <v>178</v>
       </c>
@@ -21839,7 +21929,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="842" hidden="1" spans="1:7">
+    <row r="842" spans="1:7">
       <c r="A842" t="s">
         <v>178</v>
       </c>
@@ -21862,7 +21952,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="843" hidden="1" spans="1:7">
+    <row r="843" spans="1:7">
       <c r="A843" t="s">
         <v>178</v>
       </c>
@@ -21885,7 +21975,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="844" hidden="1" spans="1:7">
+    <row r="844" spans="1:7">
       <c r="A844" t="s">
         <v>178</v>
       </c>
@@ -21908,7 +21998,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="845" hidden="1" spans="1:7">
+    <row r="845" spans="1:7">
       <c r="A845" t="s">
         <v>178</v>
       </c>
@@ -21931,7 +22021,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="846" hidden="1" spans="1:7">
+    <row r="846" spans="1:7">
       <c r="A846" t="s">
         <v>178</v>
       </c>
@@ -22069,7 +22159,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="852" hidden="1" spans="1:7">
+    <row r="852" spans="1:7">
       <c r="A852" t="s">
         <v>178</v>
       </c>
@@ -22092,7 +22182,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="853" hidden="1" spans="1:7">
+    <row r="853" spans="1:7">
       <c r="A853" t="s">
         <v>178</v>
       </c>
@@ -22115,7 +22205,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="854" hidden="1" spans="1:7">
+    <row r="854" spans="1:7">
       <c r="A854" t="s">
         <v>178</v>
       </c>
@@ -22138,7 +22228,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="855" hidden="1" spans="1:7">
+    <row r="855" spans="1:7">
       <c r="A855" t="s">
         <v>178</v>
       </c>
@@ -22161,7 +22251,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="856" hidden="1" spans="1:7">
+    <row r="856" spans="1:7">
       <c r="A856" t="s">
         <v>178</v>
       </c>
@@ -22253,7 +22343,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="860" hidden="1" spans="1:7">
+    <row r="860" spans="1:7">
       <c r="A860" t="s">
         <v>178</v>
       </c>
@@ -22276,7 +22366,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="861" hidden="1" spans="1:7">
+    <row r="861" spans="1:7">
       <c r="A861" t="s">
         <v>178</v>
       </c>
@@ -22299,7 +22389,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="862" hidden="1" spans="1:7">
+    <row r="862" spans="1:7">
       <c r="A862" t="s">
         <v>178</v>
       </c>
@@ -22460,7 +22550,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="869" hidden="1" spans="1:7">
+    <row r="869" spans="1:7">
       <c r="A869" t="s">
         <v>178</v>
       </c>
@@ -22483,7 +22573,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="870" hidden="1" spans="1:7">
+    <row r="870" spans="1:7">
       <c r="A870" t="s">
         <v>178</v>
       </c>
@@ -22506,7 +22596,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="871" hidden="1" spans="1:7">
+    <row r="871" spans="1:7">
       <c r="A871" t="s">
         <v>178</v>
       </c>
@@ -22529,7 +22619,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="872" hidden="1" spans="1:7">
+    <row r="872" spans="1:7">
       <c r="A872" t="s">
         <v>178</v>
       </c>
@@ -22552,7 +22642,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="873" hidden="1" spans="1:7">
+    <row r="873" spans="1:7">
       <c r="A873" t="s">
         <v>178</v>
       </c>
@@ -22575,7 +22665,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="874" hidden="1" spans="1:7">
+    <row r="874" spans="1:7">
       <c r="A874" t="s">
         <v>178</v>
       </c>
@@ -22621,7 +22711,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="876" hidden="1" spans="1:7">
+    <row r="876" spans="1:7">
       <c r="A876" t="s">
         <v>179</v>
       </c>
@@ -22644,7 +22734,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="877" hidden="1" spans="1:7">
+    <row r="877" spans="1:7">
       <c r="A877" t="s">
         <v>179</v>
       </c>
@@ -22667,7 +22757,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="878" hidden="1" spans="1:7">
+    <row r="878" spans="1:7">
       <c r="A878" t="s">
         <v>179</v>
       </c>
@@ -22690,7 +22780,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="879" hidden="1" spans="1:7">
+    <row r="879" spans="1:7">
       <c r="A879" t="s">
         <v>179</v>
       </c>
@@ -22713,7 +22803,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="880" hidden="1" spans="1:7">
+    <row r="880" spans="1:7">
       <c r="A880" t="s">
         <v>179</v>
       </c>
@@ -22736,7 +22826,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="881" hidden="1" spans="1:7">
+    <row r="881" spans="1:7">
       <c r="A881" t="s">
         <v>179</v>
       </c>
@@ -22851,7 +22941,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="886" hidden="1" spans="1:7">
+    <row r="886" spans="1:7">
       <c r="A886" t="s">
         <v>179</v>
       </c>
@@ -22897,7 +22987,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="888" hidden="1" spans="1:7">
+    <row r="888" spans="1:7">
       <c r="A888" t="s">
         <v>179</v>
       </c>
@@ -22920,7 +23010,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="889" hidden="1" spans="1:7">
+    <row r="889" spans="1:7">
       <c r="A889" t="s">
         <v>179</v>
       </c>
@@ -22966,7 +23056,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="891" hidden="1" spans="1:7">
+    <row r="891" spans="1:7">
       <c r="A891" t="s">
         <v>179</v>
       </c>
@@ -22989,7 +23079,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="892" hidden="1" spans="1:7">
+    <row r="892" spans="1:7">
       <c r="A892" t="s">
         <v>179</v>
       </c>
@@ -23035,7 +23125,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="894" hidden="1" spans="1:7">
+    <row r="894" spans="1:7">
       <c r="A894" t="s">
         <v>179</v>
       </c>
@@ -23058,7 +23148,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="895" hidden="1" spans="1:7">
+    <row r="895" spans="1:7">
       <c r="A895" t="s">
         <v>179</v>
       </c>
@@ -23104,7 +23194,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="897" hidden="1" spans="1:7">
+    <row r="897" spans="1:7">
       <c r="A897" t="s">
         <v>179</v>
       </c>
@@ -23127,7 +23217,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="898" hidden="1" spans="1:7">
+    <row r="898" spans="1:7">
       <c r="A898" t="s">
         <v>179</v>
       </c>
@@ -23150,7 +23240,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="899" hidden="1" spans="1:7">
+    <row r="899" spans="1:7">
       <c r="A899" t="s">
         <v>179</v>
       </c>
@@ -23173,7 +23263,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="900" hidden="1" spans="1:7">
+    <row r="900" spans="1:7">
       <c r="A900" t="s">
         <v>179</v>
       </c>
@@ -23334,7 +23424,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="907" hidden="1" spans="1:7">
+    <row r="907" spans="1:7">
       <c r="A907" t="s">
         <v>179</v>
       </c>
@@ -23357,7 +23447,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="908" hidden="1" spans="1:7">
+    <row r="908" spans="1:7">
       <c r="A908" t="s">
         <v>179</v>
       </c>
@@ -23380,7 +23470,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="909" hidden="1" spans="1:7">
+    <row r="909" spans="1:7">
       <c r="A909" t="s">
         <v>179</v>
       </c>
@@ -23403,7 +23493,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="910" hidden="1" spans="1:7">
+    <row r="910" spans="1:7">
       <c r="A910" t="s">
         <v>179</v>
       </c>
@@ -23426,7 +23516,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="911" hidden="1" spans="1:7">
+    <row r="911" spans="1:7">
       <c r="A911" t="s">
         <v>179</v>
       </c>
@@ -23449,7 +23539,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="912" hidden="1" spans="1:7">
+    <row r="912" spans="1:7">
       <c r="A912" t="s">
         <v>179</v>
       </c>
@@ -23495,7 +23585,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="914" hidden="1" spans="1:7">
+    <row r="914" spans="1:7">
       <c r="A914" t="s">
         <v>180</v>
       </c>
@@ -23518,7 +23608,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="915" hidden="1" spans="1:7">
+    <row r="915" spans="1:7">
       <c r="A915" t="s">
         <v>180</v>
       </c>
@@ -23541,7 +23631,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="916" hidden="1" spans="1:7">
+    <row r="916" spans="1:7">
       <c r="A916" t="s">
         <v>180</v>
       </c>
@@ -23564,7 +23654,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="917" hidden="1" spans="1:7">
+    <row r="917" spans="1:7">
       <c r="A917" t="s">
         <v>180</v>
       </c>
@@ -23587,7 +23677,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="918" hidden="1" spans="1:7">
+    <row r="918" spans="1:7">
       <c r="A918" t="s">
         <v>180</v>
       </c>
@@ -23610,7 +23700,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="919" hidden="1" spans="1:7">
+    <row r="919" spans="1:7">
       <c r="A919" t="s">
         <v>180</v>
       </c>
@@ -23633,7 +23723,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="920" hidden="1" spans="1:7">
+    <row r="920" spans="1:7">
       <c r="A920" t="s">
         <v>180</v>
       </c>
@@ -23794,7 +23884,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="927" hidden="1" spans="1:7">
+    <row r="927" spans="1:7">
       <c r="A927" t="s">
         <v>180</v>
       </c>
@@ -23840,7 +23930,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="929" hidden="1" spans="1:7">
+    <row r="929" spans="1:7">
       <c r="A929" t="s">
         <v>180</v>
       </c>
@@ -23863,7 +23953,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="930" hidden="1" spans="1:7">
+    <row r="930" spans="1:7">
       <c r="A930" t="s">
         <v>180</v>
       </c>
@@ -23886,7 +23976,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="931" hidden="1" spans="1:7">
+    <row r="931" spans="1:7">
       <c r="A931" t="s">
         <v>180</v>
       </c>
@@ -23909,7 +23999,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="932" hidden="1" spans="1:7">
+    <row r="932" spans="1:7">
       <c r="A932" t="s">
         <v>180</v>
       </c>
@@ -23932,7 +24022,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="933" hidden="1" spans="1:7">
+    <row r="933" spans="1:7">
       <c r="A933" t="s">
         <v>180</v>
       </c>
@@ -23955,7 +24045,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="934" hidden="1" spans="1:7">
+    <row r="934" spans="1:7">
       <c r="A934" t="s">
         <v>180</v>
       </c>
@@ -24001,7 +24091,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="936" hidden="1" spans="1:7">
+    <row r="936" spans="1:7">
       <c r="A936" t="s">
         <v>180</v>
       </c>
@@ -24047,7 +24137,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="938" hidden="1" spans="1:7">
+    <row r="938" spans="1:7">
       <c r="A938" t="s">
         <v>180</v>
       </c>
@@ -24070,7 +24160,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="939" hidden="1" spans="1:7">
+    <row r="939" spans="1:7">
       <c r="A939" t="s">
         <v>180</v>
       </c>
@@ -24093,7 +24183,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="940" hidden="1" spans="1:7">
+    <row r="940" spans="1:7">
       <c r="A940" t="s">
         <v>180</v>
       </c>
@@ -24116,7 +24206,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="941" hidden="1" spans="1:7">
+    <row r="941" spans="1:7">
       <c r="A941" t="s">
         <v>180</v>
       </c>
@@ -24139,7 +24229,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="942" hidden="1" spans="1:7">
+    <row r="942" spans="1:7">
       <c r="A942" t="s">
         <v>180</v>
       </c>
@@ -24300,7 +24390,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="949" hidden="1" spans="1:7">
+    <row r="949" spans="1:7">
       <c r="A949" t="s">
         <v>180</v>
       </c>
@@ -24323,7 +24413,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="950" hidden="1" spans="1:7">
+    <row r="950" spans="1:7">
       <c r="A950" t="s">
         <v>180</v>
       </c>
@@ -24346,7 +24436,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="951" hidden="1" spans="1:7">
+    <row r="951" spans="1:7">
       <c r="A951" t="s">
         <v>180</v>
       </c>
@@ -24369,7 +24459,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="952" hidden="1" spans="1:7">
+    <row r="952" spans="1:7">
       <c r="A952" t="s">
         <v>180</v>
       </c>
@@ -24392,7 +24482,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="953" hidden="1" spans="1:7">
+    <row r="953" spans="1:7">
       <c r="A953" t="s">
         <v>180</v>
       </c>
@@ -24415,7 +24505,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="954" hidden="1" spans="1:7">
+    <row r="954" spans="1:7">
       <c r="A954" t="s">
         <v>180</v>
       </c>
@@ -24461,7 +24551,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="956" hidden="1" spans="1:7">
+    <row r="956" spans="1:7">
       <c r="A956" t="s">
         <v>181</v>
       </c>
@@ -24484,7 +24574,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="957" hidden="1" spans="1:7">
+    <row r="957" spans="1:7">
       <c r="A957" t="s">
         <v>181</v>
       </c>
@@ -24507,7 +24597,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="958" hidden="1" spans="1:7">
+    <row r="958" spans="1:7">
       <c r="A958" t="s">
         <v>181</v>
       </c>
@@ -24530,7 +24620,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="959" hidden="1" spans="1:7">
+    <row r="959" spans="1:7">
       <c r="A959" t="s">
         <v>181</v>
       </c>
@@ -24553,7 +24643,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="960" hidden="1" spans="1:7">
+    <row r="960" spans="1:7">
       <c r="A960" t="s">
         <v>181</v>
       </c>
@@ -24576,7 +24666,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="961" hidden="1" spans="1:7">
+    <row r="961" spans="1:7">
       <c r="A961" t="s">
         <v>181</v>
       </c>
@@ -24599,7 +24689,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="962" hidden="1" spans="1:7">
+    <row r="962" spans="1:7">
       <c r="A962" t="s">
         <v>181</v>
       </c>
@@ -24622,7 +24712,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="963" hidden="1" spans="1:7">
+    <row r="963" spans="1:7">
       <c r="A963" t="s">
         <v>181</v>
       </c>
@@ -24668,7 +24758,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="965" hidden="1" spans="1:7">
+    <row r="965" spans="1:7">
       <c r="A965" t="s">
         <v>181</v>
       </c>
@@ -24760,7 +24850,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="969" hidden="1" spans="1:7">
+    <row r="969" spans="1:7">
       <c r="A969" t="s">
         <v>181</v>
       </c>
@@ -24806,7 +24896,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="971" hidden="1" spans="1:7">
+    <row r="971" spans="1:7">
       <c r="A971" t="s">
         <v>181</v>
       </c>
@@ -24829,7 +24919,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="972" hidden="1" spans="1:7">
+    <row r="972" spans="1:7">
       <c r="A972" t="s">
         <v>181</v>
       </c>
@@ -24852,7 +24942,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="973" hidden="1" spans="1:7">
+    <row r="973" spans="1:7">
       <c r="A973" t="s">
         <v>181</v>
       </c>
@@ -24875,7 +24965,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="974" hidden="1" spans="1:7">
+    <row r="974" spans="1:7">
       <c r="A974" t="s">
         <v>181</v>
       </c>
@@ -24898,7 +24988,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="975" hidden="1" spans="1:7">
+    <row r="975" spans="1:7">
       <c r="A975" t="s">
         <v>181</v>
       </c>
@@ -24921,7 +25011,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="976" hidden="1" spans="1:7">
+    <row r="976" spans="1:7">
       <c r="A976" t="s">
         <v>181</v>
       </c>
@@ -24967,7 +25057,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="978" hidden="1" spans="1:7">
+    <row r="978" spans="1:7">
       <c r="A978" t="s">
         <v>181</v>
       </c>
@@ -25036,7 +25126,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="981" hidden="1" spans="1:7">
+    <row r="981" spans="1:7">
       <c r="A981" t="s">
         <v>181</v>
       </c>
@@ -25059,7 +25149,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="982" hidden="1" spans="1:7">
+    <row r="982" spans="1:7">
       <c r="A982" t="s">
         <v>181</v>
       </c>
@@ -25082,7 +25172,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="983" hidden="1" spans="1:7">
+    <row r="983" spans="1:7">
       <c r="A983" t="s">
         <v>181</v>
       </c>
@@ -25105,7 +25195,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="984" hidden="1" spans="1:7">
+    <row r="984" spans="1:7">
       <c r="A984" t="s">
         <v>181</v>
       </c>
@@ -25128,7 +25218,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="985" hidden="1" spans="1:7">
+    <row r="985" spans="1:7">
       <c r="A985" t="s">
         <v>181</v>
       </c>
@@ -25289,7 +25379,7 @@
         <v>0.9</v>
       </c>
     </row>
-    <row r="992" hidden="1" spans="1:7">
+    <row r="992" spans="1:7">
       <c r="A992" t="s">
         <v>181</v>
       </c>
@@ -25312,7 +25402,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="993" hidden="1" spans="1:7">
+    <row r="993" spans="1:7">
       <c r="A993" t="s">
         <v>181</v>
       </c>
@@ -25335,7 +25425,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="994" hidden="1" spans="1:7">
+    <row r="994" spans="1:7">
       <c r="A994" t="s">
         <v>181</v>
       </c>
@@ -25358,7 +25448,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="995" hidden="1" spans="1:7">
+    <row r="995" spans="1:7">
       <c r="A995" t="s">
         <v>181</v>
       </c>
@@ -25381,7 +25471,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="996" hidden="1" spans="1:7">
+    <row r="996" spans="1:7">
       <c r="A996" t="s">
         <v>181</v>
       </c>
@@ -25404,7 +25494,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="997" hidden="1" spans="1:7">
+    <row r="997" spans="1:7">
       <c r="A997" t="s">
         <v>181</v>
       </c>
@@ -25797,17 +25887,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:H1013">
-    <filterColumn colId="5">
-      <customFilters>
-        <customFilter operator="equal" val="TRUE"/>
-      </customFilters>
-    </filterColumn>
     <extLst/>
   </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
   <ignoredErrors>
-    <ignoredError sqref="A1:G1013" numberStoredAsText="1"/>
+    <ignoredError sqref="A906:G1013;E905:G905;A905:C905;A1:G904" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -25815,7 +25900,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H869"/>
+  <dimension ref="A1:H46"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75" outlineLevelCol="7"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -25844,6 +25929,668 @@
         <v>152</v>
       </c>
     </row>
+    <row r="2" spans="2:5">
+      <c r="B2" t="s">
+        <v>186</v>
+      </c>
+      <c r="C2" t="s">
+        <v>187</v>
+      </c>
+      <c r="D2" t="s">
+        <v>188</v>
+      </c>
+      <c r="E2" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5">
+      <c r="B3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C3" t="s">
+        <v>133</v>
+      </c>
+      <c r="D3" t="s">
+        <v>186</v>
+      </c>
+      <c r="E3" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5">
+      <c r="B4" t="s">
+        <v>100</v>
+      </c>
+      <c r="C4" t="s">
+        <v>101</v>
+      </c>
+      <c r="D4" t="s">
+        <v>186</v>
+      </c>
+      <c r="E4" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5">
+      <c r="B5" t="s">
+        <v>134</v>
+      </c>
+      <c r="C5" t="s">
+        <v>135</v>
+      </c>
+      <c r="D5" t="s">
+        <v>186</v>
+      </c>
+      <c r="E5" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5">
+      <c r="B6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C6" t="s">
+        <v>49</v>
+      </c>
+      <c r="D6" t="s">
+        <v>186</v>
+      </c>
+      <c r="E6" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5">
+      <c r="B7" t="s">
+        <v>104</v>
+      </c>
+      <c r="C7" t="s">
+        <v>105</v>
+      </c>
+      <c r="D7" t="s">
+        <v>186</v>
+      </c>
+      <c r="E7" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5">
+      <c r="B8" t="s">
+        <v>102</v>
+      </c>
+      <c r="C8" t="s">
+        <v>103</v>
+      </c>
+      <c r="D8" t="s">
+        <v>186</v>
+      </c>
+      <c r="E8" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5">
+      <c r="B9" t="s">
+        <v>96</v>
+      </c>
+      <c r="C9" t="s">
+        <v>97</v>
+      </c>
+      <c r="D9" t="s">
+        <v>186</v>
+      </c>
+      <c r="E9" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5">
+      <c r="B10" t="s">
+        <v>98</v>
+      </c>
+      <c r="C10" t="s">
+        <v>99</v>
+      </c>
+      <c r="D10" t="s">
+        <v>186</v>
+      </c>
+      <c r="E10" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5">
+      <c r="B11" t="s">
+        <v>108</v>
+      </c>
+      <c r="C11" t="s">
+        <v>109</v>
+      </c>
+      <c r="D11" t="s">
+        <v>186</v>
+      </c>
+      <c r="E11" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5">
+      <c r="B12" t="s">
+        <v>130</v>
+      </c>
+      <c r="C12" t="s">
+        <v>131</v>
+      </c>
+      <c r="D12" t="s">
+        <v>186</v>
+      </c>
+      <c r="E12" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5">
+      <c r="B13" t="s">
+        <v>128</v>
+      </c>
+      <c r="C13" t="s">
+        <v>129</v>
+      </c>
+      <c r="D13" t="s">
+        <v>186</v>
+      </c>
+      <c r="E13" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5">
+      <c r="B14" t="s">
+        <v>94</v>
+      </c>
+      <c r="C14" t="s">
+        <v>95</v>
+      </c>
+      <c r="D14" t="s">
+        <v>186</v>
+      </c>
+      <c r="E14" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5">
+      <c r="B15" t="s">
+        <v>110</v>
+      </c>
+      <c r="C15" t="s">
+        <v>111</v>
+      </c>
+      <c r="D15" t="s">
+        <v>186</v>
+      </c>
+      <c r="E15" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5">
+      <c r="B16" t="s">
+        <v>106</v>
+      </c>
+      <c r="C16" t="s">
+        <v>107</v>
+      </c>
+      <c r="D16" t="s">
+        <v>186</v>
+      </c>
+      <c r="E16" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="17" spans="3:5">
+      <c r="C17" t="s">
+        <v>47</v>
+      </c>
+      <c r="D17" t="s">
+        <v>186</v>
+      </c>
+      <c r="E17" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5">
+      <c r="B18" t="s">
+        <v>136</v>
+      </c>
+      <c r="C18" t="s">
+        <v>137</v>
+      </c>
+      <c r="D18" t="s">
+        <v>186</v>
+      </c>
+      <c r="E18" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5">
+      <c r="B19" t="s">
+        <v>142</v>
+      </c>
+      <c r="C19" t="s">
+        <v>143</v>
+      </c>
+      <c r="D19" t="s">
+        <v>186</v>
+      </c>
+      <c r="E19" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5">
+      <c r="B20" t="s">
+        <v>138</v>
+      </c>
+      <c r="C20" t="s">
+        <v>139</v>
+      </c>
+      <c r="D20" t="s">
+        <v>186</v>
+      </c>
+      <c r="E20" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5">
+      <c r="B21" t="s">
+        <v>50</v>
+      </c>
+      <c r="C21" t="s">
+        <v>51</v>
+      </c>
+      <c r="D21" t="s">
+        <v>186</v>
+      </c>
+      <c r="E21" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5">
+      <c r="B22" t="s">
+        <v>68</v>
+      </c>
+      <c r="C22" t="s">
+        <v>69</v>
+      </c>
+      <c r="D22" t="s">
+        <v>186</v>
+      </c>
+      <c r="E22" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="23" spans="2:5">
+      <c r="B23" t="s">
+        <v>140</v>
+      </c>
+      <c r="C23" t="s">
+        <v>141</v>
+      </c>
+      <c r="D23" t="s">
+        <v>186</v>
+      </c>
+      <c r="E23" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5">
+      <c r="B24" t="s">
+        <v>183</v>
+      </c>
+      <c r="C24" t="s">
+        <v>184</v>
+      </c>
+      <c r="D24" t="s">
+        <v>186</v>
+      </c>
+      <c r="E24" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5">
+      <c r="B25" t="s">
+        <v>132</v>
+      </c>
+      <c r="C25" t="s">
+        <v>133</v>
+      </c>
+      <c r="D25" t="s">
+        <v>188</v>
+      </c>
+      <c r="E25" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5">
+      <c r="B26" t="s">
+        <v>100</v>
+      </c>
+      <c r="C26" t="s">
+        <v>101</v>
+      </c>
+      <c r="D26" t="s">
+        <v>188</v>
+      </c>
+      <c r="E26" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="27" spans="2:5">
+      <c r="B27" t="s">
+        <v>134</v>
+      </c>
+      <c r="C27" t="s">
+        <v>135</v>
+      </c>
+      <c r="D27" t="s">
+        <v>188</v>
+      </c>
+      <c r="E27" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="28" spans="2:5">
+      <c r="B28" t="s">
+        <v>48</v>
+      </c>
+      <c r="C28" t="s">
+        <v>49</v>
+      </c>
+      <c r="D28" t="s">
+        <v>188</v>
+      </c>
+      <c r="E28" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="29" spans="2:5">
+      <c r="B29" t="s">
+        <v>104</v>
+      </c>
+      <c r="C29" t="s">
+        <v>105</v>
+      </c>
+      <c r="D29" t="s">
+        <v>188</v>
+      </c>
+      <c r="E29" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="30" spans="2:5">
+      <c r="B30" t="s">
+        <v>102</v>
+      </c>
+      <c r="C30" t="s">
+        <v>103</v>
+      </c>
+      <c r="D30" t="s">
+        <v>188</v>
+      </c>
+      <c r="E30" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="31" spans="2:5">
+      <c r="B31" t="s">
+        <v>96</v>
+      </c>
+      <c r="C31" t="s">
+        <v>97</v>
+      </c>
+      <c r="D31" t="s">
+        <v>188</v>
+      </c>
+      <c r="E31" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="32" spans="2:5">
+      <c r="B32" t="s">
+        <v>98</v>
+      </c>
+      <c r="C32" t="s">
+        <v>99</v>
+      </c>
+      <c r="D32" t="s">
+        <v>188</v>
+      </c>
+      <c r="E32" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="33" spans="2:5">
+      <c r="B33" t="s">
+        <v>108</v>
+      </c>
+      <c r="C33" t="s">
+        <v>109</v>
+      </c>
+      <c r="D33" t="s">
+        <v>188</v>
+      </c>
+      <c r="E33" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="34" spans="2:5">
+      <c r="B34" t="s">
+        <v>130</v>
+      </c>
+      <c r="C34" t="s">
+        <v>131</v>
+      </c>
+      <c r="D34" t="s">
+        <v>188</v>
+      </c>
+      <c r="E34" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="35" spans="2:5">
+      <c r="B35" t="s">
+        <v>128</v>
+      </c>
+      <c r="C35" t="s">
+        <v>129</v>
+      </c>
+      <c r="D35" t="s">
+        <v>188</v>
+      </c>
+      <c r="E35" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="36" spans="2:5">
+      <c r="B36" t="s">
+        <v>94</v>
+      </c>
+      <c r="C36" t="s">
+        <v>95</v>
+      </c>
+      <c r="D36" t="s">
+        <v>188</v>
+      </c>
+      <c r="E36" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="37" spans="2:5">
+      <c r="B37" t="s">
+        <v>110</v>
+      </c>
+      <c r="C37" t="s">
+        <v>111</v>
+      </c>
+      <c r="D37" t="s">
+        <v>188</v>
+      </c>
+      <c r="E37" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="38" spans="2:5">
+      <c r="B38" t="s">
+        <v>106</v>
+      </c>
+      <c r="C38" t="s">
+        <v>107</v>
+      </c>
+      <c r="D38" t="s">
+        <v>188</v>
+      </c>
+      <c r="E38" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="39" spans="3:5">
+      <c r="C39" t="s">
+        <v>47</v>
+      </c>
+      <c r="D39" t="s">
+        <v>188</v>
+      </c>
+      <c r="E39" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="40" spans="2:5">
+      <c r="B40" t="s">
+        <v>136</v>
+      </c>
+      <c r="C40" t="s">
+        <v>137</v>
+      </c>
+      <c r="D40" t="s">
+        <v>188</v>
+      </c>
+      <c r="E40" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="41" spans="2:5">
+      <c r="B41" t="s">
+        <v>142</v>
+      </c>
+      <c r="C41" t="s">
+        <v>143</v>
+      </c>
+      <c r="D41" t="s">
+        <v>188</v>
+      </c>
+      <c r="E41" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="42" spans="2:5">
+      <c r="B42" t="s">
+        <v>138</v>
+      </c>
+      <c r="C42" t="s">
+        <v>139</v>
+      </c>
+      <c r="D42" t="s">
+        <v>188</v>
+      </c>
+      <c r="E42" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="43" spans="2:5">
+      <c r="B43" t="s">
+        <v>50</v>
+      </c>
+      <c r="C43" t="s">
+        <v>51</v>
+      </c>
+      <c r="D43" t="s">
+        <v>188</v>
+      </c>
+      <c r="E43" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="44" spans="2:5">
+      <c r="B44" t="s">
+        <v>68</v>
+      </c>
+      <c r="C44" t="s">
+        <v>69</v>
+      </c>
+      <c r="D44" t="s">
+        <v>188</v>
+      </c>
+      <c r="E44" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="45" spans="2:5">
+      <c r="B45" t="s">
+        <v>140</v>
+      </c>
+      <c r="C45" t="s">
+        <v>141</v>
+      </c>
+      <c r="D45" t="s">
+        <v>188</v>
+      </c>
+      <c r="E45" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="46" spans="2:5">
+      <c r="B46" t="s">
+        <v>183</v>
+      </c>
+      <c r="C46" t="s">
+        <v>184</v>
+      </c>
+      <c r="D46" t="s">
+        <v>188</v>
+      </c>
+      <c r="E46" t="s">
+        <v>189</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H871"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75" outlineLevelCol="7"/>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B1" t="s">
+        <v>146</v>
+      </c>
+      <c r="C1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D1" t="s">
+        <v>148</v>
+      </c>
+      <c r="E1" t="s">
+        <v>149</v>
+      </c>
+      <c r="F1" t="s">
+        <v>150</v>
+      </c>
+      <c r="G1" t="s">
+        <v>151</v>
+      </c>
+      <c r="H1" t="s">
+        <v>152</v>
+      </c>
+    </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
         <v>153</v>
@@ -45210,371 +45957,320 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="844" spans="1:7">
-      <c r="A844" t="s">
-        <v>185</v>
-      </c>
-      <c r="B844" t="s">
-        <v>183</v>
-      </c>
+    <row r="844" spans="3:5">
       <c r="C844" t="s">
-        <v>184</v>
+        <v>47</v>
       </c>
       <c r="D844" t="s">
-        <v>46</v>
+        <v>190</v>
       </c>
       <c r="E844" t="s">
-        <v>47</v>
-      </c>
-      <c r="F844" t="b">
-        <v>1</v>
-      </c>
-      <c r="G844">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="845" spans="1:7">
-      <c r="A845" t="s">
-        <v>185</v>
-      </c>
+        <v>191</v>
+      </c>
+    </row>
+    <row r="845" spans="2:5">
       <c r="B845" t="s">
-        <v>183</v>
+        <v>132</v>
       </c>
       <c r="C845" t="s">
-        <v>184</v>
+        <v>133</v>
       </c>
       <c r="D845" t="s">
-        <v>50</v>
+        <v>82</v>
       </c>
       <c r="E845" t="s">
-        <v>51</v>
-      </c>
-      <c r="F845" t="b">
-        <v>1</v>
-      </c>
-      <c r="G845">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="846" spans="1:7">
-      <c r="A846" t="s">
-        <v>185</v>
-      </c>
+        <v>83</v>
+      </c>
+    </row>
+    <row r="846" spans="2:5">
       <c r="B846" t="s">
-        <v>183</v>
+        <v>100</v>
       </c>
       <c r="C846" t="s">
-        <v>184</v>
+        <v>101</v>
       </c>
       <c r="D846" t="s">
-        <v>136</v>
+        <v>64</v>
       </c>
       <c r="E846" t="s">
-        <v>137</v>
-      </c>
-      <c r="F846" t="b">
-        <v>1</v>
-      </c>
-      <c r="G846">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="847" spans="1:7">
-      <c r="A847" t="s">
-        <v>185</v>
-      </c>
+        <v>65</v>
+      </c>
+    </row>
+    <row r="847" spans="2:5">
       <c r="B847" t="s">
-        <v>183</v>
+        <v>134</v>
       </c>
       <c r="C847" t="s">
-        <v>184</v>
+        <v>135</v>
       </c>
       <c r="D847" t="s">
-        <v>140</v>
+        <v>60</v>
       </c>
       <c r="E847" t="s">
-        <v>141</v>
-      </c>
-      <c r="F847" t="b">
-        <v>1</v>
-      </c>
-      <c r="G847">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="848" spans="1:7">
-      <c r="A848" t="s">
-        <v>185</v>
-      </c>
+        <v>192</v>
+      </c>
+    </row>
+    <row r="848" spans="2:5">
       <c r="B848" t="s">
-        <v>183</v>
+        <v>48</v>
       </c>
       <c r="C848" t="s">
-        <v>184</v>
+        <v>49</v>
       </c>
       <c r="D848" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="E848" t="s">
-        <v>69</v>
-      </c>
-      <c r="F848" t="b">
-        <v>1</v>
-      </c>
-      <c r="G848">
-        <v>0.9</v>
+        <v>55</v>
       </c>
     </row>
     <row r="849" spans="2:5">
       <c r="B849" t="s">
-        <v>46</v>
+        <v>104</v>
       </c>
       <c r="C849" t="s">
-        <v>47</v>
+        <v>105</v>
       </c>
       <c r="D849" t="s">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="E849" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
     </row>
     <row r="850" spans="2:5">
       <c r="B850" t="s">
-        <v>48</v>
+        <v>102</v>
       </c>
       <c r="C850" t="s">
-        <v>49</v>
+        <v>103</v>
       </c>
       <c r="D850" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="E850" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
     </row>
     <row r="851" spans="2:5">
       <c r="B851" t="s">
-        <v>50</v>
+        <v>96</v>
       </c>
       <c r="C851" t="s">
-        <v>51</v>
+        <v>97</v>
       </c>
       <c r="D851" t="s">
-        <v>88</v>
+        <v>58</v>
       </c>
       <c r="E851" t="s">
-        <v>89</v>
+        <v>59</v>
       </c>
     </row>
     <row r="852" spans="2:5">
       <c r="B852" t="s">
-        <v>68</v>
+        <v>98</v>
       </c>
       <c r="C852" t="s">
-        <v>69</v>
+        <v>99</v>
       </c>
       <c r="D852" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="E852" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
     </row>
     <row r="853" spans="2:5">
       <c r="B853" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="C853" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="D853" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
       <c r="E853" t="s">
-        <v>59</v>
+        <v>75</v>
       </c>
     </row>
     <row r="854" spans="2:5">
       <c r="B854" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C854" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="D854" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="E854" t="s">
-        <v>61</v>
+        <v>81</v>
       </c>
     </row>
     <row r="855" spans="2:5">
       <c r="B855" t="s">
-        <v>98</v>
+        <v>128</v>
       </c>
       <c r="C855" t="s">
-        <v>99</v>
+        <v>129</v>
       </c>
       <c r="D855" t="s">
-        <v>62</v>
+        <v>78</v>
       </c>
       <c r="E855" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
     </row>
     <row r="856" spans="2:5">
       <c r="B856" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="C856" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="D856" t="s">
-        <v>64</v>
+        <v>193</v>
       </c>
       <c r="E856" t="s">
-        <v>65</v>
+        <v>194</v>
       </c>
     </row>
     <row r="857" spans="2:5">
       <c r="B857" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="C857" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="D857" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="E857" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
     </row>
     <row r="858" spans="2:5">
       <c r="B858" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C858" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D858" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E858" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="859" spans="2:5">
-      <c r="B859" t="s">
-        <v>106</v>
-      </c>
+        <v>73</v>
+      </c>
+    </row>
+    <row r="859" spans="3:5">
       <c r="C859" t="s">
-        <v>107</v>
+        <v>47</v>
       </c>
       <c r="D859" t="s">
-        <v>72</v>
+        <v>52</v>
       </c>
       <c r="E859" t="s">
-        <v>73</v>
+        <v>53</v>
       </c>
     </row>
     <row r="860" spans="2:5">
       <c r="B860" t="s">
-        <v>108</v>
+        <v>136</v>
       </c>
       <c r="C860" t="s">
-        <v>109</v>
+        <v>137</v>
       </c>
       <c r="D860" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="E860" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
     </row>
     <row r="861" spans="2:5">
       <c r="B861" t="s">
-        <v>110</v>
+        <v>142</v>
       </c>
       <c r="C861" t="s">
-        <v>111</v>
+        <v>143</v>
       </c>
       <c r="D861" t="s">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="E861" t="s">
-        <v>77</v>
+        <v>195</v>
       </c>
     </row>
     <row r="862" spans="2:5">
       <c r="B862" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="C862" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="D862" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="E862" t="s">
-        <v>79</v>
+        <v>196</v>
       </c>
     </row>
     <row r="863" spans="2:5">
       <c r="B863" t="s">
-        <v>130</v>
+        <v>50</v>
       </c>
       <c r="C863" t="s">
-        <v>131</v>
+        <v>51</v>
       </c>
       <c r="D863" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="E863" t="s">
-        <v>81</v>
+        <v>197</v>
       </c>
     </row>
     <row r="864" spans="2:5">
       <c r="B864" t="s">
-        <v>132</v>
+        <v>68</v>
       </c>
       <c r="C864" t="s">
-        <v>133</v>
+        <v>69</v>
       </c>
       <c r="D864" t="s">
-        <v>82</v>
+        <v>56</v>
       </c>
       <c r="E864" t="s">
-        <v>83</v>
+        <v>57</v>
       </c>
     </row>
     <row r="865" spans="2:5">
       <c r="B865" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="C865" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="D865" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E865" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="866" spans="2:5">
       <c r="B866" t="s">
-        <v>138</v>
+        <v>183</v>
       </c>
       <c r="C866" t="s">
-        <v>139</v>
+        <v>184</v>
       </c>
       <c r="D866" t="s">
-        <v>90</v>
+        <v>198</v>
       </c>
       <c r="E866" t="s">
-        <v>91</v>
+        <v>199</v>
       </c>
     </row>
     <row r="867" spans="2:5">
@@ -45585,35 +46281,1590 @@
         <v>141</v>
       </c>
       <c r="D867" t="s">
-        <v>86</v>
+        <v>200</v>
       </c>
       <c r="E867" t="s">
-        <v>87</v>
+        <v>201</v>
       </c>
     </row>
     <row r="868" spans="2:5">
       <c r="B868" t="s">
+        <v>50</v>
+      </c>
+      <c r="C868" t="s">
+        <v>51</v>
+      </c>
+      <c r="D868" t="s">
+        <v>202</v>
+      </c>
+      <c r="E868" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="869" spans="2:5">
+      <c r="B869" t="s">
+        <v>136</v>
+      </c>
+      <c r="C869" t="s">
+        <v>137</v>
+      </c>
+      <c r="D869" t="s">
+        <v>204</v>
+      </c>
+      <c r="E869" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="870" spans="2:5">
+      <c r="B870" t="s">
+        <v>183</v>
+      </c>
+      <c r="C870" t="s">
+        <v>184</v>
+      </c>
+      <c r="D870" t="s">
+        <v>206</v>
+      </c>
+      <c r="E870" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="871" spans="3:5">
+      <c r="C871" t="s">
+        <v>47</v>
+      </c>
+      <c r="D871" t="s">
+        <v>208</v>
+      </c>
+      <c r="E871" t="s">
+        <v>209</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H78"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75" outlineLevelCol="7"/>
+  <cols>
+    <col min="1" max="1" width="8.75" customWidth="1"/>
+    <col min="2" max="2" width="81.875" customWidth="1"/>
+    <col min="3" max="3" width="7.5" customWidth="1"/>
+    <col min="4" max="4" width="117.875" customWidth="1"/>
+    <col min="5" max="5" width="10.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="16.5" spans="1:8">
+      <c r="A1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B1" t="s">
+        <v>146</v>
+      </c>
+      <c r="C1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D1" t="s">
+        <v>148</v>
+      </c>
+      <c r="E1" t="s">
+        <v>149</v>
+      </c>
+      <c r="F1" t="s">
+        <v>150</v>
+      </c>
+      <c r="G1" t="s">
+        <v>151</v>
+      </c>
+      <c r="H1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="2" ht="16.5" spans="2:5">
+      <c r="B2" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="3" ht="16.5" spans="2:5">
+      <c r="B3" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="4" ht="16.5" spans="2:5">
+      <c r="B4" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="5" ht="16.5" spans="2:5">
+      <c r="B5" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="6" ht="16.5" spans="2:5">
+      <c r="B6" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="7" ht="16.5" spans="2:5">
+      <c r="B7" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8" ht="32.25" spans="2:5">
+      <c r="B8" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="9" ht="32.25" spans="2:5">
+      <c r="B9" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="10" ht="16.5" spans="2:5">
+      <c r="B10" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="11" ht="16.5" spans="2:5">
+      <c r="B11" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="12" ht="16.5" spans="2:5">
+      <c r="B12" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="13" ht="16.5" spans="2:5">
+      <c r="B13" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="14" ht="16.5" spans="2:5">
+      <c r="B14" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="15" ht="16.5" spans="2:5">
+      <c r="B15" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="16" ht="16.5" spans="2:5">
+      <c r="B16" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="17" ht="16.5" spans="2:5">
+      <c r="B17" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="18" ht="16.5" spans="2:5">
+      <c r="B18" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="19" ht="16.5" spans="2:5">
+      <c r="B19" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="20" ht="16.5" spans="2:5">
+      <c r="B20" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="21" ht="16.5" spans="2:5">
+      <c r="B21" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D21" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="C868" t="s">
+      <c r="E21" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="D868" t="s">
+    </row>
+    <row r="22" ht="16.5" spans="2:5">
+      <c r="B22" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="23" ht="16.5" spans="2:5">
+      <c r="B23" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="24" ht="16.5" spans="2:5">
+      <c r="B24" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="25" ht="16.5" spans="2:5">
+      <c r="B25" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="26" ht="16.5" spans="2:5">
+      <c r="B26" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="27" ht="16.5" spans="2:5">
+      <c r="B27" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="28" ht="16.5" spans="2:5">
+      <c r="B28" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="29" ht="16.5" spans="2:5">
+      <c r="B29" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="30" ht="16.5" spans="2:5">
+      <c r="B30" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="31" ht="16.5" spans="2:5">
+      <c r="B31" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="32" ht="16.5" spans="2:5">
+      <c r="B32" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="33" ht="16.5" spans="2:5">
+      <c r="B33" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="34" ht="16.5" spans="2:5">
+      <c r="B34" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="35" ht="16.5" spans="2:5">
+      <c r="B35" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="36" ht="16.5" spans="2:5">
+      <c r="B36" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="37" ht="16.5" spans="2:5">
+      <c r="B37" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D37" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="E868" t="s">
+      <c r="E37" s="1" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="869" spans="3:5">
-      <c r="C869" t="s">
+    <row r="38" ht="16.5" spans="2:5">
+      <c r="B38" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="39" ht="16.5" spans="2:5">
+      <c r="B39" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="40" ht="16.5" spans="2:5">
+      <c r="B40" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="41" ht="16.5" spans="2:5">
+      <c r="B41" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="42" ht="16.5" spans="2:5">
+      <c r="B42" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="43" ht="16.5" spans="2:5">
+      <c r="B43" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="44" ht="16.5" spans="2:5">
+      <c r="B44" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="45" ht="16.5" spans="2:5">
+      <c r="B45" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="46" ht="16.5" spans="2:5">
+      <c r="B46" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="47" ht="16.5" spans="2:5">
+      <c r="B47" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="48" ht="16.5" spans="2:5">
+      <c r="B48" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="49" ht="16.5" spans="2:5">
+      <c r="B49" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="50" ht="16.5" spans="2:5">
+      <c r="B50" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="51" ht="16.5" spans="2:5">
+      <c r="B51" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="52" ht="16.5" spans="2:5">
+      <c r="B52" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D52" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="53" ht="16.5" spans="2:5">
+      <c r="B53" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="54" ht="16.5" spans="2:5">
+      <c r="B54" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E54" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="55" ht="16.5" spans="2:5">
+      <c r="B55" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D55" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="56" ht="16.5" spans="2:5">
+      <c r="B56" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D56" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="57" ht="16.5" spans="2:5">
+      <c r="B57" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="58" ht="16.5" spans="2:5">
+      <c r="B58" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="59" ht="16.5" spans="2:5">
+      <c r="B59" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="60" ht="16.5" spans="2:5">
+      <c r="B60" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C60" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D60" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="61" ht="16.5" spans="2:5">
+      <c r="B61" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C61" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="62" ht="16.5" spans="2:5">
+      <c r="B62" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="63" ht="16.5" spans="2:5">
+      <c r="B63" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="64" ht="16.5" spans="2:5">
+      <c r="B64" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="65" ht="16.5" spans="2:5">
+      <c r="B65" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="C65" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="66" ht="16.5" spans="2:5">
+      <c r="B66" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="D66" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="67" ht="16.5" spans="2:5">
+      <c r="B67" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="68" ht="16.5" spans="2:5">
+      <c r="B68" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="69" ht="16.5" spans="2:5">
+      <c r="B69" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="70" ht="16.5" spans="2:5">
+      <c r="B70" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="71" ht="16.5" spans="2:5">
+      <c r="B71" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C71" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="72" ht="16.5" spans="2:5">
+      <c r="B72" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="C72" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="73" spans="2:4">
+      <c r="B73" t="s">
+        <v>183</v>
+      </c>
+      <c r="D73" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="74" spans="2:5">
+      <c r="B74" t="s">
+        <v>140</v>
+      </c>
+      <c r="C74" t="s">
+        <v>141</v>
+      </c>
+      <c r="D74" t="s">
+        <v>200</v>
+      </c>
+      <c r="E74" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="75" spans="2:5">
+      <c r="B75" t="s">
+        <v>50</v>
+      </c>
+      <c r="C75" t="s">
+        <v>51</v>
+      </c>
+      <c r="D75" t="s">
+        <v>202</v>
+      </c>
+      <c r="E75" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="76" spans="2:5">
+      <c r="B76" t="s">
+        <v>136</v>
+      </c>
+      <c r="C76" t="s">
+        <v>137</v>
+      </c>
+      <c r="D76" t="s">
+        <v>204</v>
+      </c>
+      <c r="E76" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="77" spans="2:5">
+      <c r="B77" t="s">
+        <v>183</v>
+      </c>
+      <c r="C77" t="s">
+        <v>184</v>
+      </c>
+      <c r="D77" t="s">
+        <v>206</v>
+      </c>
+      <c r="E77" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="78" spans="3:5">
+      <c r="C78" t="s">
         <v>47</v>
       </c>
-      <c r="D869" t="s">
+      <c r="D78" t="s">
+        <v>208</v>
+      </c>
+      <c r="E78" t="s">
+        <v>209</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E24"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.75" outlineLevelCol="4"/>
+  <cols>
+    <col min="1" max="1" width="81.25" customWidth="1"/>
+    <col min="4" max="4" width="113.125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B1" t="s">
+        <v>146</v>
+      </c>
+      <c r="C1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C2" t="s">
+        <v>133</v>
+      </c>
+      <c r="D2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
+        <v>154</v>
+      </c>
+      <c r="B3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E3" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>155</v>
+      </c>
+      <c r="B4" t="s">
+        <v>134</v>
+      </c>
+      <c r="C4" t="s">
+        <v>135</v>
+      </c>
+      <c r="D4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E4" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>156</v>
+      </c>
+      <c r="B5" t="s">
+        <v>48</v>
+      </c>
+      <c r="C5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D5" t="s">
+        <v>54</v>
+      </c>
+      <c r="E5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
+        <v>157</v>
+      </c>
+      <c r="B6" t="s">
+        <v>104</v>
+      </c>
+      <c r="C6" t="s">
+        <v>105</v>
+      </c>
+      <c r="D6" t="s">
+        <v>70</v>
+      </c>
+      <c r="E6" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" t="s">
+        <v>158</v>
+      </c>
+      <c r="B7" t="s">
+        <v>102</v>
+      </c>
+      <c r="C7" t="s">
+        <v>103</v>
+      </c>
+      <c r="D7" t="s">
+        <v>66</v>
+      </c>
+      <c r="E7" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" t="s">
+        <v>159</v>
+      </c>
+      <c r="B8" t="s">
+        <v>96</v>
+      </c>
+      <c r="C8" t="s">
+        <v>97</v>
+      </c>
+      <c r="D8" t="s">
+        <v>58</v>
+      </c>
+      <c r="E8" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" t="s">
+        <v>160</v>
+      </c>
+      <c r="B9" t="s">
+        <v>98</v>
+      </c>
+      <c r="C9" t="s">
+        <v>99</v>
+      </c>
+      <c r="D9" t="s">
+        <v>62</v>
+      </c>
+      <c r="E9" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" t="s">
+        <v>161</v>
+      </c>
+      <c r="B10" t="s">
+        <v>108</v>
+      </c>
+      <c r="C10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D10" t="s">
+        <v>74</v>
+      </c>
+      <c r="E10" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" t="s">
+        <v>162</v>
+      </c>
+      <c r="B11" t="s">
+        <v>130</v>
+      </c>
+      <c r="C11" t="s">
+        <v>131</v>
+      </c>
+      <c r="D11" t="s">
+        <v>80</v>
+      </c>
+      <c r="E11" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" t="s">
+        <v>163</v>
+      </c>
+      <c r="B12" t="s">
+        <v>128</v>
+      </c>
+      <c r="C12" t="s">
+        <v>129</v>
+      </c>
+      <c r="D12" t="s">
+        <v>78</v>
+      </c>
+      <c r="E12" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" t="s">
+        <v>164</v>
+      </c>
+      <c r="B13" t="s">
+        <v>94</v>
+      </c>
+      <c r="C13" t="s">
+        <v>95</v>
+      </c>
+      <c r="D13" t="s">
+        <v>193</v>
+      </c>
+      <c r="E13" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" t="s">
+        <v>171</v>
+      </c>
+      <c r="B14" t="s">
+        <v>110</v>
+      </c>
+      <c r="C14" t="s">
+        <v>111</v>
+      </c>
+      <c r="D14" t="s">
+        <v>76</v>
+      </c>
+      <c r="E14" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" t="s">
+        <v>172</v>
+      </c>
+      <c r="B15" t="s">
+        <v>106</v>
+      </c>
+      <c r="C15" t="s">
+        <v>107</v>
+      </c>
+      <c r="D15" t="s">
+        <v>72</v>
+      </c>
+      <c r="E15" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" t="s">
+        <v>173</v>
+      </c>
+      <c r="C16" t="s">
+        <v>47</v>
+      </c>
+      <c r="D16" t="s">
+        <v>52</v>
+      </c>
+      <c r="E16" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" t="s">
+        <v>176</v>
+      </c>
+      <c r="B17" t="s">
+        <v>136</v>
+      </c>
+      <c r="C17" t="s">
+        <v>137</v>
+      </c>
+      <c r="D17" t="s">
+        <v>84</v>
+      </c>
+      <c r="E17" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" t="s">
+        <v>177</v>
+      </c>
+      <c r="B18" t="s">
+        <v>142</v>
+      </c>
+      <c r="C18" t="s">
+        <v>143</v>
+      </c>
+      <c r="D18" t="s">
+        <v>92</v>
+      </c>
+      <c r="E18" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" t="s">
+        <v>178</v>
+      </c>
+      <c r="B19" t="s">
+        <v>138</v>
+      </c>
+      <c r="C19" t="s">
+        <v>139</v>
+      </c>
+      <c r="D19" t="s">
+        <v>90</v>
+      </c>
+      <c r="E19" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" t="s">
+        <v>179</v>
+      </c>
+      <c r="B20" t="s">
+        <v>50</v>
+      </c>
+      <c r="C20" t="s">
+        <v>51</v>
+      </c>
+      <c r="D20" t="s">
+        <v>88</v>
+      </c>
+      <c r="E20" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" t="s">
+        <v>180</v>
+      </c>
+      <c r="B21" t="s">
+        <v>68</v>
+      </c>
+      <c r="C21" t="s">
+        <v>69</v>
+      </c>
+      <c r="D21" t="s">
+        <v>56</v>
+      </c>
+      <c r="E21" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" t="s">
+        <v>181</v>
+      </c>
+      <c r="B22" t="s">
+        <v>140</v>
+      </c>
+      <c r="C22" t="s">
+        <v>141</v>
+      </c>
+      <c r="D22" t="s">
+        <v>86</v>
+      </c>
+      <c r="E22" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" t="s">
+        <v>182</v>
+      </c>
+      <c r="B23" t="s">
+        <v>183</v>
+      </c>
+      <c r="C23" t="s">
+        <v>184</v>
+      </c>
+      <c r="D23" t="s">
+        <v>198</v>
+      </c>
+      <c r="E23" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" t="s">
+        <v>210</v>
+      </c>
+      <c r="B24" t="s">
         <v>186</v>
       </c>
-      <c r="E869" t="s">
+      <c r="C24" t="s">
         <v>187</v>
+      </c>
+      <c r="D24" t="s">
+        <v>188</v>
+      </c>
+      <c r="E24" t="s">
+        <v>189</v>
       </c>
     </row>
   </sheetData>
